--- a/business_surveys/033_microfinance_awareness_survey--business_surveys.xlsx
+++ b/business_surveys/033_microfinance_awareness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>microfinance_officer</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Microfinance Officer</t>
+          <t>Researcher</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>contact_person_title_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t>1_week</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>1 week</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1_week</t>
+          <t>2_weeks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>2 weeks</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2_weeks</t>
+          <t>3_weeks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2 weeks</t>
+          <t>3 weeks</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3_weeks</t>
+          <t>4_weeks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3 weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4_weeks</t>
+          <t>5_weeks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>5 weeks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5_weeks</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5 weeks</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1590,27 +1590,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
